--- a/Result/profitability/3669.xlsx
+++ b/Result/profitability/3669.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.95625</v>
       </c>
       <c r="N2" t="n">
-        <v>57.72625</v>
+        <v>58.14375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>4.88</v>
       </c>
       <c r="M3" t="n">
-        <v>1.47875</v>
+        <v>1.53625</v>
       </c>
       <c r="N3" t="n">
-        <v>57.40375</v>
+        <v>57.395</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7075</v>
+        <v>1.79375</v>
       </c>
       <c r="N4" t="n">
-        <v>56.0925</v>
+        <v>55.97625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.42</v>
       </c>
       <c r="M5" t="n">
-        <v>2.00875</v>
+        <v>2.15</v>
       </c>
       <c r="N5" t="n">
-        <v>55.77625</v>
+        <v>56.245</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>98.2</v>
@@ -1137,10 +1137,10 @@
         <v>4.56</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6325</v>
+        <v>2.63375</v>
       </c>
       <c r="N6" t="n">
-        <v>55.975</v>
+        <v>56.435</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.97</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7925</v>
+        <v>2.7725</v>
       </c>
       <c r="N7" t="n">
-        <v>56.04625</v>
+        <v>56.63125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>2.9675</v>
       </c>
       <c r="N8" t="n">
-        <v>56.535</v>
+        <v>56.625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9445,6 +9445,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3669</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>713</v>
+      </c>
+      <c r="D72" t="n">
+        <v>276</v>
+      </c>
+      <c r="E72" t="n">
+        <v>437</v>
+      </c>
+      <c r="F72" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="G72" t="n">
+        <v>81</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>11.33%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>83</v>
+      </c>
+      <c r="K72" t="n">
+        <v>65</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.4337500000000001</v>
+      </c>
+      <c r="N72" t="n">
+        <v>59.44375</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.720000000000006</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.01187726822830748</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-2.627906976744186</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.06511547143601315</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
